--- a/artfynd/A 41386-2023 artfynd.xlsx
+++ b/artfynd/A 41386-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365996</v>
       </c>
       <c r="B2" t="n">
-        <v>92273</v>
+        <v>92280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136365997</v>
       </c>
       <c r="B3" t="n">
-        <v>58825</v>
+        <v>58830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41386-2023 artfynd.xlsx
+++ b/artfynd/A 41386-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365996</v>
       </c>
       <c r="B2" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41386-2023 artfynd.xlsx
+++ b/artfynd/A 41386-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136365996</v>
       </c>
       <c r="B2" t="n">
-        <v>92281</v>
+        <v>92294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,48 +807,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136365997</v>
+        <v>136397154</v>
       </c>
       <c r="B3" t="n">
-        <v>58830</v>
+        <v>92294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>1588</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rännträsket, Vb</t>
+          <t>Rännträsket, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704471</v>
+        <v>704024</v>
       </c>
       <c r="R3" t="n">
-        <v>7220329</v>
+        <v>7220275</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,22 +898,821 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Felix Gustafsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gustafsson, Alva Danielsson</t>
+          <t>Alva Danielsson, Felix Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136397154</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136397162</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92294</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rännträsket, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>704341</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7220333</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136397162</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136397157</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rännträsket, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>704099</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7220255</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136397157</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136397158</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rännträsket, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>704227</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7220253</v>
+      </c>
+      <c r="S6" t="n">
+        <v>13</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136397158</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136397161</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rännträsket, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>704257</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7220274</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136397161</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136365997</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58843</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rännträsket, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>704471</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7220329</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Felix Gustafsson, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136365997</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136397156</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80063</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rännträsket, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>704056</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7220271</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136397156</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136397155</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79496</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rännträsket, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>704028</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7220285</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136397155</t>
         </is>
       </c>
     </row>
@@ -921,6 +1720,13 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41386-2023 artfynd.xlsx
+++ b/artfynd/A 41386-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136365996</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136397154</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>136397162</v>
       </c>
       <c r="B4" t="n">
-        <v>92294</v>
+        <v>92295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>136397157</v>
       </c>
       <c r="B5" t="n">
-        <v>79497</v>
+        <v>79498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136397158</v>
       </c>
       <c r="B6" t="n">
-        <v>79497</v>
+        <v>79498</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>136397161</v>
       </c>
       <c r="B7" t="n">
-        <v>79497</v>
+        <v>79498</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>136397156</v>
       </c>
       <c r="B9" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136397155</v>
       </c>
       <c r="B10" t="n">
-        <v>79496</v>
+        <v>79497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
